--- a/WorkBot/refactor/data/orders/US Foods/US Foods_Downtown_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/US Foods/US Foods_Downtown_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,66 +716,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1143849</t>
+          <t>1667864</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apple Cider (Gal)</t>
+          <t>Employee Water</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>23.43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1667864</t>
+          <t>4688660</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Employee Water</t>
+          <t>Hals - Black Cherry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>17.80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4688660</t>
+          <t>4858587</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hals - Black Cherry</t>
+          <t>Hals - Original</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,79 +797,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4858587</t>
+          <t>1138748</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hals - Original</t>
+          <t>Nirvana Water - 1.5 Liter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.80</t>
+          <t>33.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1138748</t>
+          <t>9128745</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nirvana Water - 1.5 Liter</t>
+          <t>PKT Hot Sauce - Texas Pete</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>9128745</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PKT Hot Sauce - Texas Pete</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>34.36</t>
         </is>
